--- a/documentation/planning previsionel.xlsx
+++ b/documentation/planning previsionel.xlsx
@@ -184,9 +184,6 @@
     <t>Client</t>
   </si>
   <si>
-    <t>Base de donnée</t>
-  </si>
-  <si>
     <t>Java</t>
   </si>
   <si>
@@ -199,9 +196,6 @@
     <t>Connexion db/base de donnée</t>
   </si>
   <si>
-    <t>Connexion GU</t>
-  </si>
-  <si>
     <t>Init DB</t>
   </si>
   <si>
@@ -224,6 +218,12 @@
   </si>
   <si>
     <t>Document Fonctionnel</t>
+  </si>
+  <si>
+    <t>Base de donnée et interface graphique</t>
+  </si>
+  <si>
+    <t>Connexion GU et MainGu</t>
   </si>
 </sst>
 </file>
@@ -2500,7 +2500,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="36"/>
       <c r="D8" s="42"/>
@@ -2575,7 +2575,7 @@
         <v>34</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9" s="44">
         <f>Début_Projet</f>
@@ -2652,10 +2652,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" s="44">
         <f>E9</f>
@@ -2730,10 +2730,10 @@
     <row r="11" spans="1:63" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="29"/>
       <c r="B11" s="56" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D11" s="44">
         <f>D10</f>
@@ -2810,7 +2810,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C12" s="37"/>
       <c r="D12" s="45"/>
@@ -2880,10 +2880,10 @@
     <row r="13" spans="1:63" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="30"/>
       <c r="B13" s="57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D13" s="47">
         <f>D10+7</f>
@@ -2958,10 +2958,10 @@
     <row r="14" spans="1:63" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="29"/>
       <c r="B14" s="57" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D14" s="47">
         <v>46130</v>
@@ -3035,10 +3035,10 @@
     <row r="15" spans="1:63" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="29"/>
       <c r="B15" s="57" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="59" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" s="47">
         <f>D13</f>
@@ -3111,7 +3111,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C16" s="38"/>
       <c r="D16" s="48"/>
@@ -3181,10 +3181,10 @@
     <row r="17" spans="1:63" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="29"/>
       <c r="B17" s="60" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C17" s="61" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D17" s="50">
         <f>E15+1</f>
@@ -3259,10 +3259,10 @@
     <row r="18" spans="1:63" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="29"/>
       <c r="B18" s="60" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D18" s="50">
         <f>D17</f>
@@ -3497,35 +3497,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3813,34 +3784,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3859,4 +3832,31 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>